--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,116 +2165,235 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>45993.83333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Grêmio</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Fluminense</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>45993.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -948,10 +948,10 @@
         <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45993.6875</v>
+        <v>45993.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45993.69791666666</v>
+        <v>45993.6875</v>
       </c>
     </row>
     <row r="11">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45993.70833333334</v>
+        <v>45993.69791666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45993.71875</v>
+        <v>45993.70833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45993.79166666666</v>
+        <v>45993.71875</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45993.83333333334</v>
+        <v>45993.79166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,116 +2284,235 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>45993.83333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Grêmio</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Fluminense</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="3" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>45993.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>3.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB4" t="n">
         <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -1144,40 +1144,40 @@
         <v>3.59</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA6" t="n">
         <v>2.08</v>
@@ -1186,22 +1186,22 @@
         <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.70833333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1501,40 +1501,40 @@
         <v>1.65</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.7</v>
@@ -1543,22 +1543,22 @@
         <v>2.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.6875</v>
@@ -1620,40 +1620,40 @@
         <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1.95</v>
@@ -1662,22 +1662,22 @@
         <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -2096,40 +2096,40 @@
         <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
         <v>1.65</v>
@@ -2138,22 +2138,22 @@
         <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.71875</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>4.49</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
         <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>2.47</v>
@@ -924,46 +924,46 @@
         <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
         <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1254,43 +1254,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
         <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
         <v>1.48</v>
@@ -1299,28 +1299,28 @@
         <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="P9" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>3.79</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>5.65</v>
+        <v>6.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.14</v>
+        <v>2.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.84</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2099,28 +2099,28 @@
         <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
         <v>4.33</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2141,19 +2141,19 @@
         <v>2.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.71875</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2453,40 +2453,40 @@
         <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA17" t="n">
         <v>2.2</v>
@@ -2495,22 +2495,22 @@
         <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.48</v>
+        <v>3.91</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.74</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.35</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45993.6875</v>
+        <v>45993.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45993.69791666666</v>
+        <v>45993.6875</v>
       </c>
     </row>
     <row r="12">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45993.70833333334</v>
+        <v>45993.69791666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.73</v>
       </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
         <v>4.33</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45993.71875</v>
+        <v>45993.70833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,27 +2165,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45993.79166666666</v>
+        <v>45993.71875</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="M16" t="n">
-        <v>3.51</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>4.14</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45993.83333333334</v>
+        <v>45993.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,75 +2444,194 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
         <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>45993.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z18" t="n">
         <v>2.76</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA18" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB18" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC18" t="n">
         <v>4.2</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD18" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG18" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH18" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45993.41666666666</v>
+        <v>45993.375</v>
       </c>
     </row>
     <row r="4">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>2.48</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>3.79</v>
       </c>
       <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.48</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.79</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9</v>
+        <v>5.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>2.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45993.79166666666</v>
+        <v>45993.75</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>45993.83333333334</v>
+        <v>45993.79166666666</v>
       </c>
     </row>
     <row r="18">

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="P4" t="n">
         <v>1.94</v>
@@ -915,19 +915,19 @@
         <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
         <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
         <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
@@ -936,34 +936,34 @@
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
         <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.51</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
         <v>2.6</v>
@@ -1046,43 +1046,43 @@
         <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
         <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.15</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
-        <v>2.48</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.79</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>6.9</v>
+        <v>5.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>2.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>2.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>3.79</v>
       </c>
       <c r="R11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -903,10 +903,10 @@
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="P4" t="n">
         <v>1.94</v>
@@ -918,13 +918,13 @@
         <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.47</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
         <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
         <v>7.4</v>
@@ -945,7 +945,7 @@
         <v>2.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
         <v>3.58</v>
@@ -954,16 +954,16 @@
         <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.64</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.91</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>3.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
@@ -1629,7 +1629,7 @@
         <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
         <v>3.3</v>
@@ -1653,7 +1653,7 @@
         <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
         <v>1.7</v>
@@ -1662,19 +1662,19 @@
         <v>2.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
         <v>1.17</v>
@@ -1739,40 +1739,40 @@
         <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="AA11" t="n">
         <v>1.95</v>
@@ -1781,22 +1781,22 @@
         <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
         <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1977,7 +1977,7 @@
         <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
         <v>2.06</v>
@@ -1986,16 +1986,16 @@
         <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
         <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>7</v>
@@ -2007,10 +2007,10 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
         <v>2.02</v>
@@ -2019,19 +2019,19 @@
         <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AD13" t="n">
         <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
         <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
         <v>1.79</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
-        <v>4.13</v>
+        <v>3.95</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
@@ -2117,16 +2117,16 @@
         <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z14" t="n">
         <v>5.8</v>
@@ -2135,25 +2135,25 @@
         <v>1.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.70833333334</v>
@@ -2218,7 +2218,7 @@
         <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>4.33</v>
@@ -2227,16 +2227,16 @@
         <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.1</v>
@@ -2245,10 +2245,10 @@
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
         <v>1.65</v>
@@ -2263,16 +2263,16 @@
         <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45993.71875</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
         <v>3.2</v>
@@ -2584,28 +2584,28 @@
         <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
         <v>2.2</v>
@@ -2614,22 +2614,22 @@
         <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.56</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>9.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.09</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.37</v>
+        <v>2.9</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1382,13 +1382,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
         <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
@@ -1397,10 +1397,10 @@
         <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
         <v>8.5</v>
@@ -1409,31 +1409,31 @@
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
         <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD8" t="n">
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG8" t="n">
         <v>1.28</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>2.56</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
         <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -1641,7 +1641,7 @@
         <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.11</v>
@@ -1656,10 +1656,10 @@
         <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
         <v>2.7</v>
@@ -1677,7 +1677,7 @@
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1733,10 +1733,10 @@
         <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="O11" t="n">
         <v>2.5</v>
@@ -1754,16 +1754,16 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
@@ -1772,25 +1772,25 @@
         <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
         <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG11" t="n">
         <v>1.29</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,49 +1968,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>3.73</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>1.96</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>2.02</v>
@@ -2019,22 +2019,22 @@
         <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="O14" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -2114,7 +2114,7 @@
         <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V14" t="n">
         <v>4.65</v>
@@ -2141,16 +2141,16 @@
         <v>2.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
       <c r="O15" t="n">
         <v>2.3</v>
@@ -2227,7 +2227,7 @@
         <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
         <v>2.33</v>
@@ -2251,22 +2251,22 @@
         <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AD15" t="n">
         <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
         <v>1.25</v>
@@ -2325,52 +2325,52 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
         <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
         <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
         <v>1.72</v>
@@ -2382,13 +2382,13 @@
         <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.85</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>2.56</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.15</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.42</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>5.09</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.9</v>
+        <v>1.37</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>3.25</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.56</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>3.54</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>9.15</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.09</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>2.9</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.4</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>3.82</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>5.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.82</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.73</v>
+        <v>1.94</v>
       </c>
       <c r="M13" t="n">
         <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
         <v>3.4</v>
@@ -2343,7 +2343,7 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
         <v>2.83</v>
@@ -2358,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2367,7 +2367,7 @@
         <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
         <v>2.07</v>
@@ -2376,16 +2376,16 @@
         <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
         <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
         <v>1.3</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2566,19 +2566,19 @@
         <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P18" t="n">
         <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R18" t="n">
         <v>1.46</v>
@@ -2590,10 +2590,10 @@
         <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
         <v>1.01</v>
@@ -2608,10 +2608,10 @@
         <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>
@@ -2620,7 +2620,7 @@
         <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
         <v>1.84</v>
@@ -2629,7 +2629,7 @@
         <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="R7" t="n">
         <v>1.54</v>
@@ -1281,7 +1281,7 @@
         <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
         <v>7.9</v>
@@ -1299,10 +1299,10 @@
         <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
         <v>5.09</v>
@@ -1311,13 +1311,13 @@
         <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
         <v>1.37</v>
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.15</v>
+        <v>8.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
         <v>7.1</v>
@@ -1528,37 +1528,37 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AF9" t="n">
         <v>1.32</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
         <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
         <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB10" t="n">
         <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1733,28 +1733,28 @@
         <v>5.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="P11" t="n">
         <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
         <v>1.53</v>
@@ -1772,13 +1772,13 @@
         <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
         <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AC11" t="n">
         <v>2.7</v>
@@ -1793,7 +1793,7 @@
         <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
         <v>1.18</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -2114,10 +2114,10 @@
         <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.19</v>
@@ -2129,7 +2129,7 @@
         <v>1.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA14" t="n">
         <v>1.43</v>
@@ -2138,19 +2138,19 @@
         <v>2.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.23</v>
+        <v>4.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V15" t="n">
         <v>5.8</v>
@@ -2254,19 +2254,19 @@
         <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AG15" t="n">
         <v>1.25</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="O17" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2563,31 +2563,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="O18" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="P18" t="n">
         <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="U18" t="n">
         <v>1.31</v>
@@ -2596,40 +2596,40 @@
         <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.09</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
         <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
         <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
@@ -1293,34 +1293,34 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.09</v>
+        <v>3.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.5</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.55</v>
-      </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>2.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>2.89</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>3.54</v>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.84</v>
+        <v>3.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>5.09</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.68</v>
+        <v>2.07</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.32</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.89</v>
+        <v>1.37</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="O4" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
         <v>7.4</v>
@@ -936,31 +936,31 @@
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
         <v>1.27</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1254,28 +1254,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
         <v>3.12</v>
@@ -1293,34 +1293,34 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.84</v>
+        <v>3.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>5.09</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.68</v>
+        <v>2.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.89</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.54</v>
+        <v>1.92</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.67</v>
+        <v>9.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.09</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
         <v>3.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
         <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
         <v>2.35</v>
@@ -1748,7 +1748,7 @@
         <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
@@ -1760,7 +1760,7 @@
         <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="W11" t="n">
         <v>1.11</v>
@@ -1769,19 +1769,19 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
         <v>1.44</v>
@@ -1790,13 +1790,13 @@
         <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>2.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
         <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>2.25</v>
@@ -2221,22 +2221,22 @@
         <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
         <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="U15" t="n">
         <v>1.51</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="W15" t="n">
         <v>1.1</v>
@@ -2245,34 +2245,34 @@
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>2.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45993.71875</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P17" t="n">
         <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="R17" t="n">
         <v>1.38</v>
@@ -2468,49 +2468,49 @@
         <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
         <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2563,28 +2563,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
         <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
         <v>3.35</v>
@@ -2593,13 +2593,13 @@
         <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
         <v>1.34</v>
@@ -2608,28 +2608,28 @@
         <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="AD18" t="n">
         <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
@@ -1293,34 +1293,34 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>5.09</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
         <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>1.92</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.46</v>
+        <v>9.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.09</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.92</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
         <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.95</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.15</v>
+        <v>3.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
@@ -2114,13 +2114,13 @@
         <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
@@ -2132,22 +2132,22 @@
         <v>5.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD14" t="n">
         <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AG14" t="n">
         <v>1.25</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>3.87</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2343,10 +2343,10 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>2.98</v>
@@ -2355,7 +2355,7 @@
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2367,7 +2367,7 @@
         <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
         <v>2.07</v>
@@ -2379,7 +2379,7 @@
         <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
         <v>1.91</v>
@@ -2388,10 +2388,10 @@
         <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45993.75</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>4.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
         <v>3.05</v>
@@ -936,22 +936,22 @@
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
         <v>1.87</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O4" t="n">
         <v>4.25</v>
@@ -942,16 +942,16 @@
         <v>3.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
         <v>1.87</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>2.67</v>
@@ -1061,10 +1061,10 @@
         <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>3.58</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>1.92</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.46</v>
+        <v>9.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.09</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>1.92</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
@@ -1531,34 +1531,34 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>5.09</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
         <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1623,10 +1623,10 @@
         <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -1635,13 +1635,13 @@
         <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
         <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="W10" t="n">
         <v>1.11</v>
@@ -1653,7 +1653,7 @@
         <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
         <v>1.7</v>
@@ -1671,13 +1671,13 @@
         <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1754,10 +1754,10 @@
         <v>2.76</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
         <v>7.5</v>
@@ -1787,10 +1787,10 @@
         <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
         <v>1.36</v>
@@ -1977,28 +1977,28 @@
         <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
         <v>4.33</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
         <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
@@ -2007,10 +2007,10 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="AA13" t="n">
         <v>1.81</v>
@@ -2019,22 +2019,22 @@
         <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2105,10 +2105,10 @@
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T14" t="n">
         <v>2.05</v>
@@ -2120,7 +2120,7 @@
         <v>4.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
@@ -2144,16 +2144,16 @@
         <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF14" t="n">
         <v>2.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.70833333334</v>
@@ -2218,10 +2218,10 @@
         <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1.35</v>
@@ -2462,7 +2462,7 @@
         <v>4.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
         <v>2.81</v>
@@ -2486,7 +2486,7 @@
         <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AA17" t="n">
         <v>1.9</v>
@@ -2498,7 +2498,7 @@
         <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
         <v>1.7</v>
@@ -2578,22 +2578,22 @@
         <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.01</v>
@@ -2614,22 +2614,22 @@
         <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="AD18" t="n">
         <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -897,70 +897,70 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>3.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
         <v>2.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
         <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
         <v>3.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AH4" t="n">
         <v>1.27</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="O5" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1040,7 +1040,7 @@
         <v>2.59</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="U5" t="n">
         <v>1.33</v>
@@ -1049,40 +1049,40 @@
         <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
         <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC5" t="n">
         <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
@@ -1278,31 +1278,31 @@
         <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
         <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC7" t="n">
         <v>4</v>
@@ -1311,16 +1311,16 @@
         <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.5</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
@@ -1412,34 +1412,34 @@
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.82</v>
+        <v>5.09</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
@@ -1531,34 +1531,34 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.09</v>
+        <v>3.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AG9" t="n">
         <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.46</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>5.65</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>4.57</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.16</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.87</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.95</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>3.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
         <v>2.59</v>
@@ -2105,7 +2105,7 @@
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S14" t="n">
         <v>3.7</v>
@@ -2114,16 +2114,16 @@
         <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
         <v>4.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.07</v>
@@ -2135,13 +2135,13 @@
         <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AE14" t="n">
         <v>1.4</v>
@@ -2150,10 +2150,10 @@
         <v>2.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.70833333334</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="O15" t="n">
         <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
         <v>1.35</v>
@@ -2233,7 +2233,7 @@
         <v>2.33</v>
       </c>
       <c r="U15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
         <v>6.05</v>
@@ -2251,16 +2251,16 @@
         <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
         <v>1.62</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2343,16 +2343,16 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
         <v>7.1</v>
@@ -2367,7 +2367,7 @@
         <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA16" t="n">
         <v>2.07</v>
@@ -2388,10 +2388,10 @@
         <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45993.75</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.91</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.09</v>
-      </c>
       <c r="Q7" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB7" t="n">
         <v>1.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.84</v>
+        <v>1.41</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
         <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>2.84</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>4.57</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>4.16</v>
       </c>
       <c r="N10" t="n">
-        <v>3.46</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>2.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.57</v>
+        <v>2.17</v>
       </c>
       <c r="M11" t="n">
-        <v>4.16</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>3.46</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>2.62</v>
@@ -2462,10 +2462,10 @@
         <v>4.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="T17" t="n">
         <v>2.69</v>
@@ -2474,37 +2474,37 @@
         <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC17" t="n">
         <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AG17" t="n">
         <v>1.32</v>
@@ -2563,28 +2563,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
         <v>3.15</v>
@@ -2593,28 +2593,28 @@
         <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
         <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AD18" t="n">
         <v>1.18</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.56</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>1.94</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.67</v>
+        <v>10.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.09</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>3.15</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.699999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.64</v>
+        <v>2.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.84</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P10" t="n">
         <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -1665,16 +1665,16 @@
         <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
         <v>1.18</v>
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="O11" t="n">
         <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
         <v>2.88</v>
@@ -1760,31 +1760,31 @@
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
         <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
         <v>1.8</v>
@@ -1793,7 +1793,7 @@
         <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
         <v>1.74</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
         <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
@@ -2108,16 +2108,16 @@
         <v>1.19</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T14" t="n">
         <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="W14" t="n">
         <v>1.17</v>
@@ -2129,19 +2129,19 @@
         <v>1.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
         <v>1.4</v>
@@ -2150,10 +2150,10 @@
         <v>2.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.70833333334</v>
@@ -2209,19 +2209,19 @@
         <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
         <v>1.35</v>
@@ -2233,7 +2233,7 @@
         <v>2.33</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
         <v>6.05</v>
@@ -2272,7 +2272,7 @@
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45993.71875</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2343,28 +2343,28 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
         <v>2.9</v>
@@ -2373,13 +2373,13 @@
         <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
         <v>1.91</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
         <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
@@ -1293,34 +1293,34 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.83</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.82</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
@@ -1531,34 +1531,34 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.44</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>3.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.8</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2447,7 +2447,7 @@
         <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="N17" t="n">
         <v>3.55</v>
@@ -2465,7 +2465,7 @@
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
         <v>2.69</v>
@@ -2477,7 +2477,7 @@
         <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
@@ -2489,28 +2489,28 @@
         <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
         <v>1.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD17" t="n">
         <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
         <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2563,28 +2563,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
         <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
         <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
         <v>3.15</v>
@@ -2596,7 +2596,7 @@
         <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1.06</v>
@@ -2605,31 +2605,31 @@
         <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
         <v>2.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="AD18" t="n">
         <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
         <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>2.47</v>
@@ -1537,16 +1537,16 @@
         <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
         <v>3.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
         <v>1.83</v>
@@ -1555,7 +1555,7 @@
         <v>1.86</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
         <v>1.41</v>
@@ -1614,10 +1614,10 @@
         <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>4.95</v>
@@ -1656,10 +1656,10 @@
         <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>2.8</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>3.52</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>2.5</v>
@@ -1775,10 +1775,10 @@
         <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>3.25</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
         <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="R13" t="n">
         <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="U13" t="n">
         <v>1.39</v>
@@ -2001,40 +2001,40 @@
         <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
         <v>3.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
         <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.74</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>2.2</v>
@@ -2251,10 +2251,10 @@
         <v>4.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>2.68</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>2.62</v>
@@ -2489,10 +2489,10 @@
         <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
         <v>3.35</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>3.5</v>
@@ -2608,10 +2608,10 @@
         <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>3.96</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O4" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
         <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.45</v>
+        <v>9.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.22</v>
       </c>
-      <c r="V7" t="n">
-        <v>11</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.94</v>
+        <v>3.42</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.1</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="T8" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1501,7 +1501,7 @@
         <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
         <v>2.08</v>
@@ -1510,7 +1510,7 @@
         <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
         <v>2.47</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>4.95</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>5.8</v>
+        <v>6.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.95</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>3.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2218,37 +2218,37 @@
         <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>4.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
         <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
         <v>1.65</v>
@@ -2272,7 +2272,7 @@
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45993.71875</v>
@@ -2453,37 +2453,37 @@
         <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
         <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
         <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
         <v>3.3</v>
@@ -2498,19 +2498,19 @@
         <v>3.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AG17" t="n">
         <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2572,10 +2572,10 @@
         <v>2.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
         <v>3.25</v>
@@ -2590,10 +2590,10 @@
         <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.01</v>
@@ -2602,10 +2602,10 @@
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
         <v>2.2</v>
@@ -2614,22 +2614,22 @@
         <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AD18" t="n">
         <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
         <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45993.54166666666</v>
+        <v>45993.4375</v>
       </c>
     </row>
     <row r="6">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45993.60416666666</v>
+        <v>45993.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.82</v>
+        <v>4.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>6.95</v>
+        <v>7.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.55</v>
+        <v>2.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45993.6875</v>
+        <v>45993.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>4.95</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>4.95</v>
       </c>
       <c r="P12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4.35</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45993.69791666666</v>
+        <v>45993.6875</v>
       </c>
     </row>
     <row r="13">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.95</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>3.87</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.2</v>
+        <v>4.46</v>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>4.65</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.8</v>
+        <v>3.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.09</v>
+        <v>3.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.96</v>
+        <v>1.26</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45993.70833333334</v>
+        <v>45993.69791666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.04</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45993.71875</v>
+        <v>45993.70833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
       <c r="Q16" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
         <v>4</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.48</v>
+        <v>2.68</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45993.75</v>
+        <v>45993.71875</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>45993.79166666666</v>
+        <v>45993.75</v>
       </c>
     </row>
     <row r="18">
@@ -2522,116 +2522,235 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>45993.79166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Grêmio</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Fluminense</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>2.6</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>3.1</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>2.75</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>3.58</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>3.25</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1.47</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>2.5</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>3.15</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1.31</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>8.6</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>1.01</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y19" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z19" t="n">
         <v>3</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA19" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC19" t="n">
         <v>3.95</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD19" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE19" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AF19" t="n">
         <v>1.84</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG19" t="n">
         <v>1.48</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH19" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AI19" s="3" t="n">
         <v>45993.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>4.25</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>4.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>2.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.73</v>
+        <v>3.38</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.25</v>
+        <v>2.01</v>
       </c>
       <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.2</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="AB5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.3</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH5" t="n">
-        <v>2.21</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42</v>
+        <v>1.93</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>9.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.44</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.93</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.1</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.33</v>
       </c>
-      <c r="V9" t="n">
-        <v>9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z9" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.04</v>
+        <v>3.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
         <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
         <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.83</v>
+        <v>2.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.82</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>4.95</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.3</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
@@ -2462,55 +2462,55 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
         <v>2.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AD17" t="n">
         <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
         <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.75</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
@@ -1037,40 +1037,40 @@
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
         <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
         <v>1.87</v>
@@ -1079,10 +1079,10 @@
         <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>1.93</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.1</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.33</v>
       </c>
-      <c r="V8" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.04</v>
+        <v>3.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.12</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.82</v>
+        <v>4.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>3.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>4.46</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.35</v>
+        <v>2.61</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.46</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.61</v>
+        <v>4.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
         <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -698,16 +698,16 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>2.33</v>
@@ -915,10 +915,10 @@
         <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="T4" t="n">
         <v>2.6</v>
@@ -939,7 +939,7 @@
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
         <v>1.67</v>
@@ -954,13 +954,13 @@
         <v>1.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
         <v>1.8</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="M5" t="n">
         <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
@@ -1034,55 +1034,55 @@
         <v>2.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="U5" t="n">
         <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.67</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>2.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.82</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.93</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
         <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.64</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>3.42</v>
+        <v>1.91</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>8.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>4.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>2.84</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1730,61 +1730,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
         <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
         <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
         <v>1.7</v>
@@ -1793,7 +1793,7 @@
         <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
         <v>1.18</v>
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
         <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
         <v>6.95</v>
@@ -1888,16 +1888,16 @@
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
         <v>3.14</v>
@@ -1909,13 +1909,13 @@
         <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1986,7 +1986,7 @@
         <v>2.61</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
         <v>2.69</v>
@@ -2096,7 +2096,7 @@
         <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="P14" t="n">
         <v>2.1</v>
@@ -2108,28 +2108,28 @@
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W14" t="n">
         <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
         <v>1.81</v>
@@ -2141,10 +2141,10 @@
         <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
         <v>1.95</v>
@@ -2153,7 +2153,7 @@
         <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2206,55 +2206,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
         <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
         <v>5.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AC15" t="n">
         <v>2</v>
@@ -2263,13 +2263,13 @@
         <v>1.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF15" t="n">
         <v>2.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2328,10 +2328,10 @@
         <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
         <v>2.2</v>
@@ -2343,55 +2343,55 @@
         <v>4.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
         <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
         <v>2.68</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45993.71875</v>
@@ -2572,13 +2572,13 @@
         <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="P18" t="n">
         <v>2.21</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
@@ -2617,10 +2617,10 @@
         <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
         <v>2.08</v>
@@ -2629,7 +2629,7 @@
         <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2733,7 +2733,7 @@
         <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AD19" t="n">
         <v>1.18</v>
@@ -2742,13 +2742,13 @@
         <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
         <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.9</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>2.69</v>
       </c>
       <c r="T8" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.36</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.84</v>
+        <v>1.37</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.83</v>
+        <v>2.14</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.31</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.14</v>
+        <v>4.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>3.24</v>
       </c>
       <c r="T12" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>2.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="O2" t="n">
         <v>2.4</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="AA2" t="n">
         <v>2.5</v>
@@ -778,49 +778,49 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.27</v>
       </c>
       <c r="AA3" t="n">
         <v>2.23</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.32</v>
       </c>
-      <c r="V8" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.84</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="R9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.14</v>
+        <v>4.83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3.24</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>2.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.83</v>
+        <v>2.14</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.31</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.87</v>
+        <v>3.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O13" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
         <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
         <v>1.39</v>
@@ -1992,7 +1992,7 @@
         <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
@@ -2004,7 +2004,7 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.28</v>
@@ -2013,22 +2013,22 @@
         <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
         <v>1.29</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="P14" t="n">
         <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.35</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2111,10 +2111,10 @@
         <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
         <v>6.65</v>
@@ -2132,19 +2132,19 @@
         <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
         <v>1.95</v>
@@ -2153,7 +2153,7 @@
         <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB17" t="n">
         <v>1.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.75</v>
@@ -2563,31 +2563,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="P18" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
         <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
         <v>1.41</v>
@@ -2608,28 +2608,28 @@
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AG18" t="n">
         <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="R19" t="n">
         <v>1.47</v>
@@ -2712,7 +2712,7 @@
         <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
@@ -2727,28 +2727,28 @@
         <v>3</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AD19" t="n">
         <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45993.89583333334</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -698,16 +698,16 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3.58</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="U4" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.45</v>
+        <v>1.89</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>3.58</v>
       </c>
       <c r="T5" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.35</v>
       </c>
-      <c r="V8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.76</v>
+        <v>3.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.32</v>
       </c>
-      <c r="V9" t="n">
-        <v>9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.84</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M10" t="n">
         <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
         <v>1.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
         <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
         <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
         <v>4.43</v>
@@ -1986,25 +1986,25 @@
         <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
         <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.28</v>
@@ -2013,25 +2013,25 @@
         <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
         <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
         <v>1.26</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
         <v>3.6</v>
@@ -2230,46 +2230,46 @@
         <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V15" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="W15" t="n">
         <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AC15" t="n">
         <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.75</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
         <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>2.66</v>
@@ -2578,16 +2578,16 @@
         <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
         <v>2.81</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U18" t="n">
         <v>1.41</v>
@@ -2602,7 +2602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
         <v>3.3</v>
@@ -2611,16 +2611,16 @@
         <v>1.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
         <v>2.04</v>
@@ -2629,7 +2629,7 @@
         <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
         <v>3.15</v>
@@ -2712,37 +2712,37 @@
         <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
         <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AD19" t="n">
         <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
         <v>1.37</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.45</v>
+        <v>1.89</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>3.58</v>
       </c>
       <c r="T4" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.58</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="U5" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
         <v>1.97</v>
@@ -1510,16 +1510,16 @@
         <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
         <v>8.5</v>
@@ -1528,37 +1528,37 @@
         <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
         <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
         <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
         <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1849,25 +1849,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
         <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
         <v>2.74</v>
@@ -1885,34 +1885,34 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
         <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
         <v>1.76</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>2.36</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>3.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.36</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>6.65</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2328,55 +2328,55 @@
         <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
         <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.04</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
         <v>1.44</v>
@@ -2388,7 +2388,7 @@
         <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
         <v>2.05</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45993.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3.58</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="U4" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.45</v>
+        <v>1.89</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>3.58</v>
       </c>
       <c r="T5" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.84</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>4.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>2.84</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>6.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.63</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>3.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.36</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>2.36</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>2.66</v>
@@ -2608,10 +2608,10 @@
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>2.99</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
         <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>3.58</v>
@@ -2727,10 +2727,10 @@
         <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>3.94</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
         <v>2.95</v>
@@ -698,16 +698,16 @@
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC2" t="n">
         <v>4.45</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.23</v>
+        <v>2.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>4.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
         <v>1.32</v>
@@ -930,40 +930,40 @@
         <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="O7" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
         <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.07</v>
@@ -1293,19 +1293,19 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
         <v>1.25</v>
@@ -1314,13 +1314,13 @@
         <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1397,10 +1397,10 @@
         <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>8.5</v>
@@ -1409,7 +1409,7 @@
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
         <v>1.35</v>
@@ -1430,13 +1430,13 @@
         <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
         <v>1.82</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
         <v>1.44</v>
@@ -1501,28 +1501,28 @@
         <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
@@ -1549,16 +1549,16 @@
         <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1668,13 +1668,13 @@
         <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
         <v>1.44</v>
@@ -1754,13 +1754,13 @@
         <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="W11" t="n">
         <v>1.07</v>
@@ -1787,7 +1787,7 @@
         <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
         <v>2.11</v>
@@ -1867,10 +1867,10 @@
         <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="T12" t="n">
         <v>2.53</v>
@@ -1879,7 +1879,7 @@
         <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
@@ -1906,10 +1906,10 @@
         <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
         <v>1.25</v>
@@ -1977,40 +1977,40 @@
         <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2019,19 +2019,19 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
         <v>1.26</v>
@@ -2096,40 +2096,40 @@
         <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
         <v>1.81</v>
@@ -2138,22 +2138,22 @@
         <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
         <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2343,31 +2343,31 @@
         <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
         <v>1.65</v>
@@ -2376,7 +2376,7 @@
         <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1.44</v>
@@ -2578,7 +2578,7 @@
         <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
@@ -2593,7 +2593,7 @@
         <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
         <v>1.06</v>
@@ -2623,13 +2623,13 @@
         <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
         <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2691,13 +2691,13 @@
         <v>2.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
         <v>1.46</v>
@@ -2706,13 +2706,13 @@
         <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
@@ -2733,7 +2733,7 @@
         <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.94</v>
+        <v>4.23</v>
       </c>
       <c r="AD19" t="n">
         <v>1.18</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45993.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45993.375</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
         <v>3.8</v>
@@ -1046,19 +1046,19 @@
         <v>1.54</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>6.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.67</v>
@@ -1067,10 +1067,10 @@
         <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1.6</v>
@@ -1079,10 +1079,10 @@
         <v>2.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.35</v>
       </c>
       <c r="Z8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH8" t="n">
         <v>2.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.01</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
         <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.9</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.63</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>3.24</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>4.42</v>
+        <v>2.37</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
         <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>3.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.37</v>
+        <v>4.42</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.1</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.18</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
         <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.95</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.6</v>
       </c>
       <c r="O15" t="n">
         <v>2.2</v>
@@ -2224,43 +2224,43 @@
         <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="n">
         <v>1.4</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="M17" t="n">
         <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
         <v>3.1</v>
@@ -2459,7 +2459,7 @@
         <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.38</v>
@@ -2468,13 +2468,13 @@
         <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
@@ -2501,16 +2501,16 @@
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.75</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,75 +2682,194 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.28</v>
+        <v>1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>9.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>2.13</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AI19" s="3" t="n">
+        <v>45993.83333333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z20" t="n">
         <v>2.8</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA20" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AB20" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AC20" t="n">
         <v>4.23</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD20" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AE20" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AF20" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG20" t="n">
         <v>1.37</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AH20" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI19" s="3" t="n">
+      <c r="AI20" s="3" t="n">
         <v>45993.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>4.96</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45993.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.39</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.11</v>
+        <v>4.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45993.375</v>
@@ -1135,67 +1135,67 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
         <v>1.33</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.44</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.9</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2.9</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>3.24</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.63</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>3.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.37</v>
+        <v>4.42</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.1</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.18</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
         <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.42</v>
+        <v>2.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
         <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
         <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
         <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
@@ -2593,7 +2593,7 @@
         <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.06</v>
@@ -2608,28 +2608,28 @@
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
         <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,194 +2682,75 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>3.01</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.17</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.55</v>
+        <v>3.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.9</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>4.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.74</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>45993.83333333334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45993</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI20" s="3" t="n">
         <v>45993.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,99 +633,99 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4.96</v>
+        <v>3.74</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45993.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.74</v>
+        <v>4.96</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AB3" t="n">
         <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45993.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="N4" t="n">
-        <v>2.01</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>4.41</v>
+        <v>2.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>3.58</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.74</v>
       </c>
-      <c r="AA4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.82</v>
+        <v>2.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>3.58</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>6.02</v>
+        <v>7.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.63</v>
+        <v>3.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>2.79</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.03</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.21</v>
+        <v>2.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="M7" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="AA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE7" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>10.07</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.44</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>2.84</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1501,31 +1501,31 @@
         <v>2.72</v>
       </c>
       <c r="O9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.1</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
@@ -1543,22 +1543,22 @@
         <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M10" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.01</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V10" t="n">
         <v>7.6</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.96</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.9</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,61 +1849,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3.24</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
         <v>1.75</v>
@@ -1912,10 +1912,10 @@
         <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1977,28 +1977,28 @@
         <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.42</v>
+        <v>4.48</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
@@ -2007,10 +2007,10 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA13" t="n">
         <v>1.98</v>
@@ -2019,16 +2019,16 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
         <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
         <v>1.29</v>
@@ -2096,40 +2096,40 @@
         <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.4</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V14" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
         <v>1.81</v>
@@ -2138,22 +2138,22 @@
         <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2337,37 +2337,37 @@
         <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>4.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
         <v>1.65</v>
@@ -2376,16 +2376,16 @@
         <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>2.65</v>
@@ -2608,10 +2608,10 @@
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>3.4</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.01</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>3.62</v>
@@ -2727,10 +2727,10 @@
         <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>4.25</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,99 +633,99 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.74</v>
+        <v>4.96</v>
       </c>
       <c r="O2" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45993.375</v>
@@ -752,99 +752,99 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4.96</v>
+        <v>3.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AB3" t="n">
         <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45993.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>3.58</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="U4" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="N5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.1</v>
       </c>
-      <c r="O5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC5" t="n">
-        <v>3.84</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>2.49</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>2.71</v>
       </c>
       <c r="N6" t="n">
-        <v>3.59</v>
+        <v>3.02</v>
       </c>
       <c r="O6" t="n">
-        <v>2.79</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.95</v>
+        <v>4.13</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>2.73</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>45993.54166666666</v>
+        <v>45993.5</v>
       </c>
     </row>
     <row r="7">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.91</v>
+        <v>4.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="U7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45993.54166666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.07</v>
+        <v>3.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>2.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.84</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>4.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.38</v>
+        <v>1.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>2.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.48</v>
+        <v>10.07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>2.84</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.15</v>
+        <v>2.53</v>
       </c>
       <c r="M10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.9</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
         <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.44</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
         <v>3.32</v>
@@ -1409,34 +1409,34 @@
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.49</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
         <v>1.39</v>
@@ -1488,38 +1488,38 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="P9" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.07</v>
+        <v>10.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
         <v>7.1</v>
@@ -1531,10 +1531,10 @@
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
         <v>2.2</v>
@@ -1543,19 +1543,19 @@
         <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
         <v>2.84</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="V10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45993.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AE11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45993.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.18</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45993.6875</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.87</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.48</v>
+        <v>2.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>4.55</v>
       </c>
       <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V13" t="n">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.24</v>
+        <v>3.91</v>
       </c>
       <c r="AD13" t="n">
         <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>3.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.39</v>
+        <v>4.54</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45993.69791666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>2.2</v>
@@ -2224,55 +2224,55 @@
         <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AD15" t="n">
         <v>1.83</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45993.70833333334</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N16" t="n">
         <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.4</v>
       </c>
       <c r="O16" t="n">
         <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.01</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
@@ -2352,16 +2352,16 @@
         <v>2.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="W16" t="n">
         <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.22</v>
@@ -2370,28 +2370,28 @@
         <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
         <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45993.71875</v>

--- a/jogos_2025-12-02.xlsx
+++ b/jogos_2025-12-02.xlsx
@@ -633,25 +633,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4.96</v>
+        <v>3.74</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45993.375</v>
@@ -752,99 +752,99 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.74</v>
+        <v>4.96</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AB3" t="n">
         <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45993.375</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,25 +871,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="N4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.1</v>
       </c>
-      <c r="O4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.84</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45993.4375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>3.58</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45993.4375</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,20 +1713,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1951,20 +1951,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.1</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
@@ -2483,34 +2483,34 @@
         <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA17" t="n">
         <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
         <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45993.75</v>
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.65</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.69</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
         <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
         <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
         <v>1.77</v>
@@ -2626,10 +2626,10 @@
         <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45993.79166666666</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
         <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.31</v>
       </c>
-      <c r="V19" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.41</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45993.89583333334</v>
